--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>L'emplacement disparait de la page. Rien n'est invente pour le combler.</t>
+          <t>Carte d'identite et bande : la case affiche « — ». Ailleurs, l'emplacement disparait. Rien n'est invente.</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>« Who we recommend [Firm] for » : verdict, bons profils, « Consider another firm if… »</t>
+          <t>« Who we recommend [Firm] for » : verdict, bons profils, « Consider another firm if… » · « Strengths and things to know » : points forts et limites</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Si sa portee n'est pas confirmee, le prix s'affiche avec « ≈ » et la mention « Estimated price — verify at checkout ».</t>
+          <t>Si sa portee n'est pas confirmee, le prix remise s'affiche avec « ≈ » devant.</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1268,18 @@
       <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Static</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>limite</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1430,7 @@
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>« Founded ». Vide : la case disparait.</t>
+          <t>« Founded ». Vide : « — ».</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1466,7 @@
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>« CEO / Founder ». Vide : la case disparait.</t>
+          <t>« CEO / Founder ». Vide : « — ».</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1538,7 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : l'etiquette disparait.</t>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
         </is>
       </c>
     </row>
@@ -12007,7 +12019,7 @@
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>non_confirmee → prix avec « ≈ » et « Estimated price — verify at checkout ».</t>
+          <t>non_confirmee → prix remise affiche avec « ≈ ». Sert aussi la reponse FAQ sur le code.</t>
         </is>
       </c>
     </row>
@@ -12043,7 +12055,7 @@
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>La mention sous le code et la reponse FAQ « Does the promotional code apply to every account? ». Slugs separes par des virgules.</t>
+          <t>Le prix remise ne s'affiche que sur ces programmes, et la reponse FAQ « Does the promotional code apply to every account? ». Slugs separes par des virgules.</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12091,7 @@
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>La mention sous le code. Vide : « no published expiry ».</t>
+          <t>Non affiche sur la page pour l'instant.</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12230,7 +12242,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>verdict = « Our verdict » · pour_qui = liste ✓ · pas_pour = « Consider another firm if… »</t>
+          <t>verdict = « Our verdict » · pour_qui = liste ✓ · pas_pour = « Consider another firm if… » · point_fort = « Strengths » · limite = « Things to know »</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
@@ -12290,14 +12302,34 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="19" t="n"/>
-      <c r="C6" s="16" t="n"/>
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>90% profit split on Elite, Nitro and Prime; 80% on Instant</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
-      <c r="B7" s="19" t="n"/>
-      <c r="C7" s="16" t="n"/>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>No financial regulator licence</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n"/>
@@ -12439,10 +12471,20 @@
       <c r="B35" s="19" t="n"/>
       <c r="C35" s="16" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="16" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A3:A35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$I$2:$I$4</formula1>
+    <dataValidation sqref="A3:A37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$I$2:$I$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12495,7 +12537,7 @@
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Verifiee, sans rien supposer. Vide : la question disparait.</t>
+          <t>Vide : la page recompose la reponse depuis les autres onglets (programmes, prix, partage, retraits, offre).</t>
         </is>
       </c>
     </row>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -836,7 +836,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>« Build your account » : les 4 selecteurs, le prix, les 4 metriques · « Rules by phase » : le tableau Evaluation / Funded</t>
+          <t>« Account configurator » : les etapes, le prix, la selection · « Rules by phase » : le tableau Evaluation / Funded</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>Le carre « FIRM LOGO ». Une image qui existe vraiment. Vide : initiale du nom.</t>
+          <t>Le logo, cliquable : il ouvre le site de la firme par ton lien d'affiliation, code promo compris. Vide : initiale du nom.</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>L'etiquette « [Market] prop firm » et « Firm type » (CFD / Futures / Both, deduit d'ici). futures, cfd — separes par une virgule si plusieurs.</t>
+          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Le paragraphe sous le nom. Factuel, 2 a 3 lignes maximum.</t>
+          <t>Le texte sous le nom. Factuel et developpe : separe les paragraphes par une ligne vide (Alt+Entree deux fois).</t>
         </is>
       </c>
     </row>
@@ -1423,10 +1423,8 @@
         </is>
       </c>
       <c r="B7" s="19" t="n"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>(vide — absente du releve)</t>
-        </is>
+      <c r="C7" s="20" t="n">
+        <v>2024</v>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
@@ -1461,7 +1459,7 @@
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>(vide — absent du releve)</t>
+          <t>Christian Habibi</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
@@ -1479,7 +1477,7 @@
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Futures</t>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
@@ -1515,7 +1513,7 @@
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>(vide — non documentes publiquement)</t>
+          <t>Credit/Debit Card, Crypto</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
@@ -1573,7 +1571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1581,7 +1579,8 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1612,6 +1611,11 @@
       </c>
       <c r="F1" s="14" t="inlineStr">
         <is>
+          <t>accroche</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
           <t>nb_plans  (auto)</t>
         </is>
       </c>
@@ -1624,12 +1628,12 @@
       </c>
       <c r="B2" s="21" t="inlineStr">
         <is>
-          <t>Bouton « 2. Choose a programme ».</t>
+          <t>Carte « How do you want to be funded? ».</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Bouton « 1. Choose a market ». Masque s'il n'y en a qu'un.</t>
+          <t>Carte « Choose your market ». Masquee s'il n'y en a qu'un.</t>
         </is>
       </c>
       <c r="D2" s="21" t="inlineStr">
@@ -1643,6 +1647,11 @@
         </is>
       </c>
       <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>Petite phrase au-dessus du nom dans « How do you want to be funded? ». Vide : le type (Evaluation / No evaluation).</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="inlineStr">
         <is>
           <t>Plans rattaches.</t>
         </is>
@@ -1674,7 +1683,8 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="22">
         <f>IF(A3="","",COUNTIF(Plans!$A$3:$A$300,A3))</f>
         <v/>
       </c>
@@ -1685,7 +1695,8 @@
       <c r="C4" s="16" t="n"/>
       <c r="D4" s="16" t="n"/>
       <c r="E4" s="16" t="n"/>
-      <c r="F4" s="22">
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="22">
         <f>IF(A4="","",COUNTIF(Plans!$A$3:$A$300,A4))</f>
         <v/>
       </c>
@@ -1696,7 +1707,8 @@
       <c r="C5" s="16" t="n"/>
       <c r="D5" s="16" t="n"/>
       <c r="E5" s="16" t="n"/>
-      <c r="F5" s="22">
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="22">
         <f>IF(A5="","",COUNTIF(Plans!$A$3:$A$300,A5))</f>
         <v/>
       </c>
@@ -1707,7 +1719,8 @@
       <c r="C6" s="16" t="n"/>
       <c r="D6" s="16" t="n"/>
       <c r="E6" s="16" t="n"/>
-      <c r="F6" s="22">
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="22">
         <f>IF(A6="","",COUNTIF(Plans!$A$3:$A$300,A6))</f>
         <v/>
       </c>
@@ -1718,7 +1731,8 @@
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
       <c r="E7" s="16" t="n"/>
-      <c r="F7" s="22">
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="22">
         <f>IF(A7="","",COUNTIF(Plans!$A$3:$A$300,A7))</f>
         <v/>
       </c>
@@ -1729,7 +1743,8 @@
       <c r="C8" s="16" t="n"/>
       <c r="D8" s="16" t="n"/>
       <c r="E8" s="16" t="n"/>
-      <c r="F8" s="22">
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="22">
         <f>IF(A8="","",COUNTIF(Plans!$A$3:$A$300,A8))</f>
         <v/>
       </c>
@@ -1740,7 +1755,8 @@
       <c r="C9" s="16" t="n"/>
       <c r="D9" s="16" t="n"/>
       <c r="E9" s="16" t="n"/>
-      <c r="F9" s="22">
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="22">
         <f>IF(A9="","",COUNTIF(Plans!$A$3:$A$300,A9))</f>
         <v/>
       </c>
@@ -1751,7 +1767,8 @@
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
-      <c r="F10" s="22">
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="22">
         <f>IF(A10="","",COUNTIF(Plans!$A$3:$A$300,A10))</f>
         <v/>
       </c>
@@ -1762,7 +1779,8 @@
       <c r="C11" s="16" t="n"/>
       <c r="D11" s="16" t="n"/>
       <c r="E11" s="16" t="n"/>
-      <c r="F11" s="22">
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="22">
         <f>IF(A11="","",COUNTIF(Plans!$A$3:$A$300,A11))</f>
         <v/>
       </c>
@@ -1773,7 +1791,8 @@
       <c r="C12" s="16" t="n"/>
       <c r="D12" s="16" t="n"/>
       <c r="E12" s="16" t="n"/>
-      <c r="F12" s="22">
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="22">
         <f>IF(A12="","",COUNTIF(Plans!$A$3:$A$300,A12))</f>
         <v/>
       </c>
@@ -1784,7 +1803,8 @@
       <c r="C13" s="16" t="n"/>
       <c r="D13" s="16" t="n"/>
       <c r="E13" s="16" t="n"/>
-      <c r="F13" s="22">
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="22">
         <f>IF(A13="","",COUNTIF(Plans!$A$3:$A$300,A13))</f>
         <v/>
       </c>
@@ -1795,7 +1815,8 @@
       <c r="C14" s="16" t="n"/>
       <c r="D14" s="16" t="n"/>
       <c r="E14" s="16" t="n"/>
-      <c r="F14" s="22">
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="22">
         <f>IF(A14="","",COUNTIF(Plans!$A$3:$A$300,A14))</f>
         <v/>
       </c>
@@ -1806,7 +1827,8 @@
       <c r="C15" s="16" t="n"/>
       <c r="D15" s="16" t="n"/>
       <c r="E15" s="16" t="n"/>
-      <c r="F15" s="22">
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="22">
         <f>IF(A15="","",COUNTIF(Plans!$A$3:$A$300,A15))</f>
         <v/>
       </c>
@@ -1817,7 +1839,8 @@
       <c r="C16" s="16" t="n"/>
       <c r="D16" s="16" t="n"/>
       <c r="E16" s="16" t="n"/>
-      <c r="F16" s="22">
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="22">
         <f>IF(A16="","",COUNTIF(Plans!$A$3:$A$300,A16))</f>
         <v/>
       </c>
@@ -1828,7 +1851,8 @@
       <c r="C17" s="16" t="n"/>
       <c r="D17" s="16" t="n"/>
       <c r="E17" s="16" t="n"/>
-      <c r="F17" s="22">
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="22">
         <f>IF(A17="","",COUNTIF(Plans!$A$3:$A$300,A17))</f>
         <v/>
       </c>
@@ -1839,7 +1863,8 @@
       <c r="C18" s="16" t="n"/>
       <c r="D18" s="16" t="n"/>
       <c r="E18" s="16" t="n"/>
-      <c r="F18" s="22">
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="22">
         <f>IF(A18="","",COUNTIF(Plans!$A$3:$A$300,A18))</f>
         <v/>
       </c>
@@ -1850,7 +1875,8 @@
       <c r="C19" s="16" t="n"/>
       <c r="D19" s="16" t="n"/>
       <c r="E19" s="16" t="n"/>
-      <c r="F19" s="22">
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="22">
         <f>IF(A19="","",COUNTIF(Plans!$A$3:$A$300,A19))</f>
         <v/>
       </c>
@@ -1861,7 +1887,8 @@
       <c r="C20" s="16" t="n"/>
       <c r="D20" s="16" t="n"/>
       <c r="E20" s="16" t="n"/>
-      <c r="F20" s="22">
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="22">
         <f>IF(A20="","",COUNTIF(Plans!$A$3:$A$300,A20))</f>
         <v/>
       </c>
@@ -1872,7 +1899,8 @@
       <c r="C21" s="16" t="n"/>
       <c r="D21" s="16" t="n"/>
       <c r="E21" s="16" t="n"/>
-      <c r="F21" s="22">
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="22">
         <f>IF(A21="","",COUNTIF(Plans!$A$3:$A$300,A21))</f>
         <v/>
       </c>
@@ -1883,7 +1911,8 @@
       <c r="C22" s="16" t="n"/>
       <c r="D22" s="16" t="n"/>
       <c r="E22" s="16" t="n"/>
-      <c r="F22" s="22">
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="22">
         <f>IF(A22="","",COUNTIF(Plans!$A$3:$A$300,A22))</f>
         <v/>
       </c>
@@ -1894,7 +1923,8 @@
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="16" t="n"/>
       <c r="E23" s="16" t="n"/>
-      <c r="F23" s="22">
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="22">
         <f>IF(A23="","",COUNTIF(Plans!$A$3:$A$300,A23))</f>
         <v/>
       </c>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -1295,7 +1295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1401,158 +1401,176 @@
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="B6" s="16" t="n"/>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Le texte sous le nom. Factuel et developpe : separe les paragraphes par une ligne vide (Alt+Entree deux fois).</t>
+          <t>En haut de page, sous le nom : 1 a 2 phrases. Le detail va dans presentation.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>annee_creation</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n"/>
-      <c r="C7" s="20" t="n">
-        <v>2024</v>
+          <t>presentation</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+        </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>« Founded ». Vide : « — ».</t>
+          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>pays</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
+          <t>annee_creation</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="20" t="n">
+        <v>2024</v>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>« Country ».</t>
+          <t>« Founded ». Vide : « — ».</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>ceo_fondateur</t>
+          <t>pays</t>
         </is>
       </c>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Christian Habibi</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>« CEO / Founder ». Vide : « — ».</t>
+          <t>« Country ».</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>actifs</t>
+          <t>ceo_fondateur</t>
         </is>
       </c>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+          <t>Christian Habibi</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>« Tradable assets » : une etiquette par actif, separes par des virgules.</t>
+          <t>« CEO / Founder ». Vide : « — ».</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>plateformes</t>
+          <t>actifs</t>
         </is>
       </c>
       <c r="B11" s="16" t="n"/>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart</t>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>« Platforms » : celles choisies A L'ACHAT, separees par des virgules.</t>
+          <t>« Tradable assets » (« Futures markets » chez une firme 100 % futures) : une etiquette par actif, separes par des virgules.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>moyens_paiement</t>
+          <t>plateformes</t>
         </is>
       </c>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Credit/Debit Card, Crypto</t>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>« Payment methods » : moyens de paiement a l'achat (carte, crypto…). Ceux des retraits vont dans Conditions &gt; retraits.</t>
+          <t>« Platforms » : toutes les plateformes prises en charge, separees par des virgules.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>levier</t>
+          <t>moyens_paiement</t>
         </is>
       </c>
       <c r="B13" s="16" t="n"/>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>(vide — futures : exposition en contrats, pas en levier)</t>
+          <t>Credit/Debit Card, Crypto</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+          <t>« Payment methods » : moyens de paiement a l'achat (carte, crypto…). Ceux des retraits vont dans Conditions &gt; retraits.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>styles_trading</t>
+          <t>levier</t>
         </is>
       </c>
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="17" t="inlineStr">
         <is>
+          <t>N/A (futures contracts)</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>styles_trading</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
           <t>(vide — absent du releve)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
         </is>
@@ -1571,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1580,7 +1598,8 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1616,6 +1635,11 @@
       </c>
       <c r="G1" s="14" t="inlineStr">
         <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
           <t>nb_plans  (auto)</t>
         </is>
       </c>
@@ -1653,6 +1677,11 @@
       </c>
       <c r="G2" s="21" t="inlineStr">
         <is>
+          <t>Carte « Which program fits you? » : une phrase vraie de CE programme. Vide : la carte n'affiche que le nom.</t>
+        </is>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
           <t>Plans rattaches.</t>
         </is>
       </c>
@@ -1683,8 +1712,17 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F3" s="17" t="n"/>
-      <c r="G3" s="22">
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>One-step evaluation</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>One-step evaluation, end-of-day drawdown and no daily loss limit.</t>
+        </is>
+      </c>
+      <c r="H3" s="22">
         <f>IF(A3="","",COUNTIF(Plans!$A$3:$A$300,A3))</f>
         <v/>
       </c>
@@ -1696,7 +1734,8 @@
       <c r="D4" s="16" t="n"/>
       <c r="E4" s="16" t="n"/>
       <c r="F4" s="16" t="n"/>
-      <c r="G4" s="22">
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="22">
         <f>IF(A4="","",COUNTIF(Plans!$A$3:$A$300,A4))</f>
         <v/>
       </c>
@@ -1708,7 +1747,8 @@
       <c r="D5" s="16" t="n"/>
       <c r="E5" s="16" t="n"/>
       <c r="F5" s="16" t="n"/>
-      <c r="G5" s="22">
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="22">
         <f>IF(A5="","",COUNTIF(Plans!$A$3:$A$300,A5))</f>
         <v/>
       </c>
@@ -1720,7 +1760,8 @@
       <c r="D6" s="16" t="n"/>
       <c r="E6" s="16" t="n"/>
       <c r="F6" s="16" t="n"/>
-      <c r="G6" s="22">
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="22">
         <f>IF(A6="","",COUNTIF(Plans!$A$3:$A$300,A6))</f>
         <v/>
       </c>
@@ -1732,7 +1773,8 @@
       <c r="D7" s="16" t="n"/>
       <c r="E7" s="16" t="n"/>
       <c r="F7" s="16" t="n"/>
-      <c r="G7" s="22">
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="22">
         <f>IF(A7="","",COUNTIF(Plans!$A$3:$A$300,A7))</f>
         <v/>
       </c>
@@ -1744,7 +1786,8 @@
       <c r="D8" s="16" t="n"/>
       <c r="E8" s="16" t="n"/>
       <c r="F8" s="16" t="n"/>
-      <c r="G8" s="22">
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="22">
         <f>IF(A8="","",COUNTIF(Plans!$A$3:$A$300,A8))</f>
         <v/>
       </c>
@@ -1756,7 +1799,8 @@
       <c r="D9" s="16" t="n"/>
       <c r="E9" s="16" t="n"/>
       <c r="F9" s="16" t="n"/>
-      <c r="G9" s="22">
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="22">
         <f>IF(A9="","",COUNTIF(Plans!$A$3:$A$300,A9))</f>
         <v/>
       </c>
@@ -1768,7 +1812,8 @@
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
       <c r="F10" s="16" t="n"/>
-      <c r="G10" s="22">
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="22">
         <f>IF(A10="","",COUNTIF(Plans!$A$3:$A$300,A10))</f>
         <v/>
       </c>
@@ -1780,7 +1825,8 @@
       <c r="D11" s="16" t="n"/>
       <c r="E11" s="16" t="n"/>
       <c r="F11" s="16" t="n"/>
-      <c r="G11" s="22">
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="22">
         <f>IF(A11="","",COUNTIF(Plans!$A$3:$A$300,A11))</f>
         <v/>
       </c>
@@ -1792,7 +1838,8 @@
       <c r="D12" s="16" t="n"/>
       <c r="E12" s="16" t="n"/>
       <c r="F12" s="16" t="n"/>
-      <c r="G12" s="22">
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="22">
         <f>IF(A12="","",COUNTIF(Plans!$A$3:$A$300,A12))</f>
         <v/>
       </c>
@@ -1804,7 +1851,8 @@
       <c r="D13" s="16" t="n"/>
       <c r="E13" s="16" t="n"/>
       <c r="F13" s="16" t="n"/>
-      <c r="G13" s="22">
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="22">
         <f>IF(A13="","",COUNTIF(Plans!$A$3:$A$300,A13))</f>
         <v/>
       </c>
@@ -1816,7 +1864,8 @@
       <c r="D14" s="16" t="n"/>
       <c r="E14" s="16" t="n"/>
       <c r="F14" s="16" t="n"/>
-      <c r="G14" s="22">
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="22">
         <f>IF(A14="","",COUNTIF(Plans!$A$3:$A$300,A14))</f>
         <v/>
       </c>
@@ -1828,7 +1877,8 @@
       <c r="D15" s="16" t="n"/>
       <c r="E15" s="16" t="n"/>
       <c r="F15" s="16" t="n"/>
-      <c r="G15" s="22">
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="22">
         <f>IF(A15="","",COUNTIF(Plans!$A$3:$A$300,A15))</f>
         <v/>
       </c>
@@ -1840,7 +1890,8 @@
       <c r="D16" s="16" t="n"/>
       <c r="E16" s="16" t="n"/>
       <c r="F16" s="16" t="n"/>
-      <c r="G16" s="22">
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="22">
         <f>IF(A16="","",COUNTIF(Plans!$A$3:$A$300,A16))</f>
         <v/>
       </c>
@@ -1852,7 +1903,8 @@
       <c r="D17" s="16" t="n"/>
       <c r="E17" s="16" t="n"/>
       <c r="F17" s="16" t="n"/>
-      <c r="G17" s="22">
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="22">
         <f>IF(A17="","",COUNTIF(Plans!$A$3:$A$300,A17))</f>
         <v/>
       </c>
@@ -1864,7 +1916,8 @@
       <c r="D18" s="16" t="n"/>
       <c r="E18" s="16" t="n"/>
       <c r="F18" s="16" t="n"/>
-      <c r="G18" s="22">
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="22">
         <f>IF(A18="","",COUNTIF(Plans!$A$3:$A$300,A18))</f>
         <v/>
       </c>
@@ -1876,7 +1929,8 @@
       <c r="D19" s="16" t="n"/>
       <c r="E19" s="16" t="n"/>
       <c r="F19" s="16" t="n"/>
-      <c r="G19" s="22">
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="22">
         <f>IF(A19="","",COUNTIF(Plans!$A$3:$A$300,A19))</f>
         <v/>
       </c>
@@ -1888,7 +1942,8 @@
       <c r="D20" s="16" t="n"/>
       <c r="E20" s="16" t="n"/>
       <c r="F20" s="16" t="n"/>
-      <c r="G20" s="22">
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="22">
         <f>IF(A20="","",COUNTIF(Plans!$A$3:$A$300,A20))</f>
         <v/>
       </c>
@@ -1900,7 +1955,8 @@
       <c r="D21" s="16" t="n"/>
       <c r="E21" s="16" t="n"/>
       <c r="F21" s="16" t="n"/>
-      <c r="G21" s="22">
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="22">
         <f>IF(A21="","",COUNTIF(Plans!$A$3:$A$300,A21))</f>
         <v/>
       </c>
@@ -1912,7 +1968,8 @@
       <c r="D22" s="16" t="n"/>
       <c r="E22" s="16" t="n"/>
       <c r="F22" s="16" t="n"/>
-      <c r="G22" s="22">
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="22">
         <f>IF(A22="","",COUNTIF(Plans!$A$3:$A$300,A22))</f>
         <v/>
       </c>
@@ -1924,7 +1981,8 @@
       <c r="D23" s="16" t="n"/>
       <c r="E23" s="16" t="n"/>
       <c r="F23" s="16" t="n"/>
-      <c r="G23" s="22">
+      <c r="G23" s="16" t="n"/>
+      <c r="H23" s="22">
         <f>IF(A23="","",COUNTIF(Plans!$A$3:$A$300,A23))</f>
         <v/>
       </c>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -14,9 +14,11 @@
     <sheet name="Phases" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Offre" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Conditions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Verdict" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="FAQ" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Listes" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="Parcours" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Couts" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Verdict" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="FAQ" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Listes" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -319,6 +321,21 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>PropFirmScanner</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Le releve FuturesElite du 7 septembre 2026 ne contient aucune FAQ : aucune reponse d'exemple n'a ete inventee.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -420,9 +437,24 @@
     <author>PropFirmScanner</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="A3" authorId="0" shapeId="0">
       <text>
-        <t>Le releve FuturesElite du 7 septembre 2026 ne contient aucune FAQ : aucune reponse d'exemple n'a ete inventee.</t>
+        <t>Exemple : valeurs reelles FuturesElite, releve du 7 septembre 2026. A remplacer.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>PropFirmScanner</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>Exemple : valeurs reelles FuturesElite, releve du 7 septembre 2026. A remplacer.</t>
       </text>
     </comment>
   </commentList>
@@ -719,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D32"/>
+  <dimension ref="B2:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -867,122 +899,114 @@
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Verdict</t>
+          <t>Parcours</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>« Who we recommend [Firm] for » : verdict, bons profils, « Consider another firm if… » · « Strengths and things to know » : points forts et limites</t>
+          <t>« From evaluation to your first payout » : les etapes, dans l'ordre</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="9" t="inlineStr">
         <is>
+          <t>Couts</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>« What you will actually pay » : le tableau des frais</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>« Who we recommend [Firm] for » : verdict, bons profils, « Consider another firm if… » · « Strengths and things to know » : points forts et limites</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>« Frequently asked questions » : les 5 questions du gabarit sont deja ecrites, il reste les reponses</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>LES REGLES QUI EVITENT LES ERREURS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Un plan, plusieurs phases</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Un plan = programme + variante + taille (onglet Plans). Ses phases Evaluation et Funded vont dans l'onglet Phases, une ligne chacune.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Un seul plan dans la carte promo</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Mets « oui » dans plan_carte_promo sur UN seul plan : c'est lui qui s'affiche dans la carte en haut de page.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="9" t="inlineStr">
         <is>
+          <t>Un plan, plusieurs phases</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Un plan = programme + variante + taille (onglet Plans). Ses phases Evaluation et Funded vont dans l'onglet Phases, une ligne chacune.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Un seul plan dans la carte promo</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Mets « oui » dans plan_carte_promo sur UN seul plan : c'est lui qui s'affiche dans la carte en haut de page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
           <t>Un code promo non confirme</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Si sa portee n'est pas confirmee, le prix remise s'affiche avec « ≈ » devant.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>CONTROLES AUTOMATIQUES</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>attendu</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Programmes</t>
-        </is>
-      </c>
-      <c r="C26" s="12">
-        <f>COUNTA(Programmes!A3:A60)</f>
-        <v/>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>≥ 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Plans (selections)</t>
-        </is>
-      </c>
-      <c r="C27" s="12">
-        <f>COUNTA(Plans!A3:A300)</f>
-        <v/>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>≥ 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Phases</t>
+          <t>Programmes</t>
         </is>
       </c>
       <c r="C28" s="12">
-        <f>COUNTA(Phases!A3:A900)</f>
+        <f>COUNTA(Programmes!A3:A60)</f>
         <v/>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -994,62 +1018,94 @@
     <row r="29">
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Plans dans la carte promo</t>
+          <t>Plans (selections)</t>
         </is>
       </c>
       <c r="C29" s="12">
-        <f>COUNTIF(Plans!F3:F300,"oui")</f>
+        <f>COUNTA(Plans!A3:A300)</f>
         <v/>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>exactement 1</t>
+          <t>≥ 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Phases sans plan correspondant</t>
+          <t>Phases</t>
         </is>
       </c>
       <c r="C30" s="12">
-        <f>COUNTIF(Phases!M3:M900,"PLAN INCONNU")</f>
+        <f>COUNTA(Phases!A3:A900)</f>
         <v/>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>≥ 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Plans sans aucune phase</t>
+          <t>Plans dans la carte promo</t>
         </is>
       </c>
       <c r="C31" s="12">
-        <f>COUNTIF(Plans!H3:H300,"aucune phase")</f>
+        <f>COUNTIF(Plans!F3:F300,"oui")</f>
         <v/>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>exactement 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
+          <t>Phases sans plan correspondant</t>
+        </is>
+      </c>
+      <c r="C32" s="12">
+        <f>COUNTIF(Phases!M3:M900,"PLAN INCONNU")</f>
+        <v/>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Plans sans aucune phase</t>
+        </is>
+      </c>
+      <c r="C33" s="12">
+        <f>COUNTIF(Plans!H3:H300,"aucune phase")</f>
+        <v/>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
           <t>Plans d'un programme inconnu</t>
         </is>
       </c>
-      <c r="C32" s="12">
+      <c r="C34" s="12">
         <f>COUNTIF(Plans!H3:H300,"programme inconnu")</f>
         <v/>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1063,11 +1119,481 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="006B7280"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>ordre</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>texte</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>verdict = « Our verdict » · pour_qui = liste ✓ · pas_pour = « Consider another firm if… » · point_fort = « Strengths » · limite = « Things to know »</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>1, 2, 3 dans chaque type. Le gabarit en montre 3.</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>Conclusion independante, sans superlatif marketing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite bets on generous terms once you are funded: up to a 90% split, daily payouts, and no funded consistency rule on Elite and Nitro. In exchange, the firm is young and is a proprietary trading company rather than a regulated broker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>pour_qui</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>A high split and frequent payouts, with no waiting period</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>pas_pour</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>You want a regulated broker: Quantum SRL holds no financial regulator licence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>90% profit split on Elite, Nitro and Prime; 80% on Instant</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>No financial regulator licence</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="16" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="16" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="16" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="16" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="16" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="16" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="16" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="16" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="16" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="16" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="16" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="16" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="n"/>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="16" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="16" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="19" t="n"/>
+      <c r="C35" s="16" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="16" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A3:A37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$J$2:$J$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="006B7280"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>ordre</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>reponse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Ordre d'affichage.</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Les 5 questions du gabarit sont pre-remplies ; [Firm] sera remplace par le nom. Tu peux en ajouter.</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>Vide : la page recompose la reponse depuis les autres onglets (programmes, prix, partage, retraits, offre).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Is [Firm] suitable for beginners?</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>How much does [Firm] cost?</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>What profit split does [Firm] offer?</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>How do payouts work?</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Does the promotional code apply to every account?</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1079,50 +1605,56 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
+          <t>etape_parcours</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
           <t>marche</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>type_programme</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>statut</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>phase</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>type_perte</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>devise</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>portee_offre</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>oui_non</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>type_verdict</t>
         </is>
@@ -1131,45 +1663,50 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
           <t>futures</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>evaluation</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>evaluation</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>End of Day</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>universelle_verifiee</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>verdict</t>
         </is>
@@ -1178,45 +1715,50 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>funded</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
           <t>cfd</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>instant</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>promotional</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>evaluation_2</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Trailing Equity</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>restreinte</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>pour_qui</t>
         </is>
@@ -1225,59 +1767,64 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
+          <t>payout</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
           <t>stocks</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>retired</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>funded</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Trailing Intraday</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>non_confirmee</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>pas_pour</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>crypto</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Static</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>point_fort</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="I6" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>limite</t>
         </is>
@@ -1990,13 +2537,13 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="C3:C23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$5</formula1>
+      <formula1>=Listes!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="D3:D23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$B$2:$B$3</formula1>
+      <formula1>=Listes!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation sqref="E3:E23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$C$2:$C$4</formula1>
+      <formula1>=Listes!$D$2:$D$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4543,10 +5090,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D3:D153" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$F$2:$F$4</formula1>
+      <formula1>=Listes!$G$2:$G$4</formula1>
     </dataValidation>
     <dataValidation sqref="F3:F153" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$H$2:$H$3</formula1>
+      <formula1>=Listes!$I$2:$I$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12010,10 +12557,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D3:D404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$D$2:$D$4</formula1>
+      <formula1>=Listes!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="G3:G404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$E$2:$E$5</formula1>
+      <formula1>=Listes!$F$2:$F$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12186,10 +12733,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$G$2:$G$4</formula1>
+      <formula1>=Listes!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$H$2:$H$3</formula1>
+      <formula1>=Listes!$I$2:$I$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12298,30 +12845,36 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B7280"/>
+    <tabColor rgb="004B5563"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>ordre</t>
         </is>
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>ordre</t>
+          <t>etape</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>texte</t>
         </is>
@@ -12330,249 +12883,161 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>verdict = « Our verdict » · pour_qui = liste ✓ · pas_pour = « Consider another firm if… » · point_fort = « Strengths » · limite = « Things to know »</t>
+          <t>1, 2, 3 : l'ordre des etapes, de gauche a droite.</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
         <is>
-          <t>1, 2, 3 dans chaque type. Le gabarit en montre 3.</t>
+          <t>evaluation, funded ou payout. Sert le petit titre au-dessus de l'etape.</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Conclusion independante, sans superlatif marketing.</t>
+          <t>Le titre de l'etape, en quelques mots.</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>Ce qui se passe a cette etape, au niveau de la firme. Les differences entre programmes restent dans « Which program fits you? ».</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="n">
+      <c r="A3" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>FuturesElite bets on generous terms once you are funded: up to a 90% split, daily payouts, and no funded consistency rule on Elite and Nitro. In exchange, the firm is young and is a proprietary trading company rather than a regulated broker.</t>
+          <t>Pass the evaluation</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>One phase on Elite, Nitro and Prime: reach the profit objective without breaching the maximum loss. There is no deadline. Minimum trading days differ by programme. Instant has no evaluation.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>pour_qui</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="n">
-        <v>1</v>
+      <c r="A4" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>funded</t>
+        </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>A high split and frequent payouts, with no waiting period</t>
+          <t>Get the funded account</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>The simulated funded account opens with no activation fee. Drawdown type and contract scaling change with the programme, so the rules table above is the one that applies.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>pas_pour</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="n">
-        <v>1</v>
+      <c r="A5" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>payout</t>
+        </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>You want a regulated broker: Quantum SRL holds no financial regulator licence.</t>
+          <t>Request your first payout</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Requests can be made every day and are reviewed in under 24 hours on average, then paid through Rise after KYC. Each request is capped by account size, and minimum trading days apply first.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>point_fort</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>90% profit split on Elite, Nitro and Prime; 80% on Instant</t>
-        </is>
-      </c>
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>No financial regulator licence</t>
-        </is>
-      </c>
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="19" t="n"/>
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="16" t="n"/>
       <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
-      <c r="B9" s="19" t="n"/>
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="16" t="n"/>
       <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="19" t="n"/>
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="16" t="n"/>
       <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="19" t="n"/>
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="16" t="n"/>
       <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="19" t="n"/>
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="16" t="n"/>
       <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="19" t="n"/>
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="16" t="n"/>
       <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="19" t="n"/>
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="19" t="n"/>
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="16" t="n"/>
       <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="19" t="n"/>
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="16" t="n"/>
       <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="19" t="n"/>
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="16" t="n"/>
       <c r="C17" s="16" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="16" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="16" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="16" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="16" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="16" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="16" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="16" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="16" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="19" t="n"/>
-      <c r="C27" s="16" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="16" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="16" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="16" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="16" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="16" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="19" t="n"/>
-      <c r="C33" s="16" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="16" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="19" t="n"/>
-      <c r="C35" s="16" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="n"/>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="16" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="n"/>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A3:A37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$I$2:$I$6</formula1>
+    <dataValidation sqref="B3:B17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12583,16 +13048,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B7280"/>
+    <tabColor rgb="004B5563"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -12603,161 +13069,213 @@
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>libelle</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
-          <t>reponse</t>
+          <t>montant</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Ordre d'affichage.</t>
+          <t>1, 2, 3 : l'ordre des lignes.</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
         <is>
-          <t>Les 5 questions du gabarit sont pre-remplies ; [Firm] sera remplace par le nom. Tu peux en ajouter.</t>
+          <t>Le nom du frais, tel qu'il s'affiche.</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Vide : la page recompose la reponse depuis les autres onglets (programmes, prix, partage, retraits, offre).</t>
+          <t>Texte libre : « $95 – $569 », « None », « Per contract ». Vide : la ligne affiche « — ».</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>Quand il se paie, et a quelle condition. Vide : rien sous le montant.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="n">
+      <c r="A3" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Is [Firm] suitable for beginners?</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="n"/>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Account purchase</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>$95 – $569</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>One-time fee per account, no monthly subscription. The price depends on programme and size.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="n">
+      <c r="A4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>How much does [Firm] cost?</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n"/>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Reset after a breach</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>$79 – $229</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Optional, on the evaluation programmes only. A new account can be bought instead.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>What profit split does [Firm] offer?</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n"/>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Funded account activation</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>No activation fee once the evaluation is passed.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>How do payouts work?</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="n"/>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Trading costs</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Per contract</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Commissions and exchange fees are charged on each executed trade.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Does the promotional code apply to every account?</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="n"/>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>First payout</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>$500 minimum on Elite</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Requests are capped from $1,000 to $3,500 by account size.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="n"/>
       <c r="B8" s="16" t="n"/>
       <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="16" t="n"/>
       <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="16" t="n"/>
       <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="n"/>
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n"/>
       <c r="B15" s="16" t="n"/>
       <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="19" t="n"/>
       <c r="B16" s="16" t="n"/>
       <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="19" t="n"/>
       <c r="B17" s="16" t="n"/>
       <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="19" t="n"/>
       <c r="B18" s="16" t="n"/>
       <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="19" t="n"/>
       <c r="B19" s="16" t="n"/>
       <c r="C19" s="16" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
